--- a/preview/pr-13/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/preview/pr-13/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:34:58+00:00</t>
+    <t>2026-09-30T07:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,31 +141,31 @@
     <t>staendig</t>
   </si>
   <si>
-    <t>Ständig</t>
+    <t>Always</t>
   </si>
   <si>
     <t>meistens</t>
   </si>
   <si>
-    <t>Meistens</t>
+    <t>Often</t>
   </si>
   <si>
     <t>manchmal</t>
   </si>
   <si>
-    <t>Manchmal</t>
+    <t>Sometimes</t>
   </si>
   <si>
     <t>selten</t>
   </si>
   <si>
-    <t>Selten</t>
+    <t>Rarely</t>
   </si>
   <si>
     <t>nie</t>
   </si>
   <si>
-    <t>Nie</t>
+    <t>Never</t>
   </si>
 </sst>
 </file>

--- a/preview/pr-13/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/preview/pr-13/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T07:33:31+00:00</t>
+    <t>2026-09-30T08:17:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-13/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/preview/pr-13/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:17:00+00:00</t>
+    <t>2026-09-30T08:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
